--- a/01_analyses_states/Arunachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Arunachal Pradesh/results/SoIB_summaries.xlsx
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="C8">
-        <v>547</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>0</v>

--- a/01_analyses_states/Arunachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Arunachal Pradesh/results/SoIB_summaries.xlsx
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C8">
-        <v>539</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>58.3</v>
+        <v>60.2</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2">
-        <v>82.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>41.7</v>
+        <v>39.8</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>17.8</v>
+        <v>19.5</v>
       </c>
     </row>
   </sheetData>
